--- a/site/Flow-Recruit-Workday-Integration-Guide/headings.xlsx
+++ b/site/Flow-Recruit-Workday-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,51 +595,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manage Candidate</t>
+          <t>Applications Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KPSRZ8DQD6WPCVEQWVWE6B02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSRZ8DQD6WPCVEQWVWE6B02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Filter Candidate</t>
+          <t>Manage Candidate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Filter Candidate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,41 +649,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Worker Management</t>
+          <t>Match Expression Correlation Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KPSSFTKW6FZCFSWA1FY472MW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSFTKW6FZCFSWA1FY472MW</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SolarWinds Service Desk Settings</t>
+          <t>Safeguard Limit Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KPSSJ4CVCV85GBK8CG864HQ5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSJ4CVCV85GBK8CG864HQ5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADP Workforce Now Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,107 +715,107 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGM450J1YK3FN478G7X08MGN</t>
+          <t>h_01KPSSKTV6TR3Q5NQM5AB20J3F</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KGM450J1YK3FN478G7X08MGN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSKTV6TR3Q5NQM5AB20J3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KPSSMYC1CBVFW5HB9X98PZT0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSMYC1CBVFW5HB9X98PZT0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KPSSXAHCYF9E3K0FT0Y6PWQ8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSXAHCYF9E3K0FT0Y6PWQ8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KPSSXRMJRM3VYB4AQ9MF87HJ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSXRMJRM3VYB4AQ9MF87HJ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>h_01KPSSYSJ3ZPV9MS749604WAKK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KMF55H58M5ND9REFBS3NRMB5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSSYSJ3ZPV9MS749604WAKK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KPSVF44VWYJ2JF610MT6PQHT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSVF44VWYJ2JF610MT6PQHT</t>
         </is>
       </c>
     </row>
@@ -886,68 +886,68 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KPSVR6EJSNBYABHKMA92MVEG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSVR6EJSNBYABHKMA92MVEG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KPSW0924GVK1JS1B0Q55W4AF</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSW0924GVK1JS1B0Q55W4AF</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Configurations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KPSW0VF30NP0QDN8BVT6PVVY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSW0VF30NP0QDN8BVT6PVVY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -969,64 +969,130 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KPSWXE8Y4J4EYZ0RHECNWSTP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSWXE8Y4J4EYZ0RHECNWSTP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KPSXSWDGBBTVS9VZEX813QQN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSXSWDGBBTVS9VZEX813QQN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KPSXSWDGA2R1CXGQ6GR265A8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01KPSXSWDGA2R1CXGQ6GR265A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Flow-Recruit-Workday-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
